--- a/Sindhi Muslim/Staff Attendance/Staff Attendance - 2nd QTR.xlsx
+++ b/Sindhi Muslim/Staff Attendance/Staff Attendance - 2nd QTR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Staff Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680272BF-7410-4C18-A9AC-46DAB6402A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6809FC13-79F4-471C-B7DD-9C3EF524A6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="51">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -182,6 +182,15 @@
   <si>
     <t>Shab-E-Baraat</t>
   </si>
+  <si>
+    <t>Urs (Lal Shahbaz Qalandar)</t>
+  </si>
+  <si>
+    <t>Kashmir Day</t>
+  </si>
+  <si>
+    <t>O.Off</t>
+  </si>
 </sst>
 </file>
 
@@ -263,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -444,19 +453,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -519,11 +515,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -550,14 +596,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -573,13 +618,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -594,18 +648,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
@@ -616,6 +658,9 @@
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -633,7 +678,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -642,11 +687,305 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="118">
+  <dxfs count="145">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2117,95 +2456,95 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="25"/>
     </row>
     <row r="3" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="18" t="str">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="17" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="E3" s="18" t="str">
+      <c r="E3" s="17" t="str">
         <f t="shared" ref="E3:P3" si="0">TEXT(E4,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="27"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="29"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2256,19 +2595,19 @@
       <c r="P4" s="7">
         <v>45626</v>
       </c>
-      <c r="Q4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="R4" s="16" t="s">
+      <c r="Q4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="S4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="T4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2300,7 +2639,7 @@
       <c r="I5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="J5" s="20" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -2334,11 +2673,11 @@
         <v>6</v>
       </c>
       <c r="T5" s="4">
-        <v>4</v>
-      </c>
-      <c r="U5" s="19">
+        <v>1</v>
+      </c>
+      <c r="U5" s="18">
         <f>Q5+S5+T5</f>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -2369,7 +2708,7 @@
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="29"/>
+      <c r="J6" s="21"/>
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2401,11 +2740,11 @@
         <v>0</v>
       </c>
       <c r="T6" s="4">
-        <v>4</v>
-      </c>
-      <c r="U6" s="19">
+        <v>1</v>
+      </c>
+      <c r="U6" s="18">
         <f t="shared" ref="U6" si="4">Q6+S6+T6</f>
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -2436,7 +2775,7 @@
       <c r="I7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="29"/>
+      <c r="J7" s="21"/>
       <c r="K7" s="4" t="s">
         <v>7</v>
       </c>
@@ -2468,11 +2807,11 @@
         <v>1</v>
       </c>
       <c r="T7" s="4">
-        <v>4</v>
-      </c>
-      <c r="U7" s="19">
+        <v>1</v>
+      </c>
+      <c r="U7" s="18">
         <f t="shared" ref="U7:U13" si="5">Q7+S7+T7</f>
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2503,7 +2842,7 @@
       <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="29"/>
+      <c r="J8" s="21"/>
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2535,11 +2874,11 @@
         <v>0</v>
       </c>
       <c r="T8" s="4">
-        <v>4</v>
-      </c>
-      <c r="U8" s="19">
+        <v>1</v>
+      </c>
+      <c r="U8" s="18">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -2570,7 +2909,7 @@
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="29"/>
+      <c r="J9" s="21"/>
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2602,11 +2941,11 @@
         <v>0</v>
       </c>
       <c r="T9" s="4">
-        <v>4</v>
-      </c>
-      <c r="U9" s="19">
+        <v>1</v>
+      </c>
+      <c r="U9" s="18">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -2637,7 +2976,7 @@
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="29"/>
+      <c r="J10" s="21"/>
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
@@ -2669,11 +3008,11 @@
         <v>0</v>
       </c>
       <c r="T10" s="4">
-        <v>4</v>
-      </c>
-      <c r="U10" s="19">
+        <v>1</v>
+      </c>
+      <c r="U10" s="18">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -2704,7 +3043,7 @@
       <c r="I11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="29"/>
+      <c r="J11" s="21"/>
       <c r="K11" s="4" t="s">
         <v>6</v>
       </c>
@@ -2736,11 +3075,11 @@
         <v>0</v>
       </c>
       <c r="T11" s="4">
-        <v>4</v>
-      </c>
-      <c r="U11" s="19">
+        <v>1</v>
+      </c>
+      <c r="U11" s="18">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -2771,7 +3110,7 @@
       <c r="I12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="29"/>
+      <c r="J12" s="21"/>
       <c r="K12" s="4" t="s">
         <v>6</v>
       </c>
@@ -2803,11 +3142,11 @@
         <v>1</v>
       </c>
       <c r="T12" s="4">
-        <v>4</v>
-      </c>
-      <c r="U12" s="19">
+        <v>1</v>
+      </c>
+      <c r="U12" s="18">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2838,7 +3177,7 @@
       <c r="I13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="30"/>
+      <c r="J13" s="22"/>
       <c r="K13" s="6" t="s">
         <v>6</v>
       </c>
@@ -2870,104 +3209,104 @@
         <v>0</v>
       </c>
       <c r="T13" s="6">
-        <v>4</v>
-      </c>
-      <c r="U13" s="20">
+        <v>1</v>
+      </c>
+      <c r="U13" s="19">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="25"/>
     </row>
     <row r="17" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="18" t="str">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="17" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="E17" s="18" t="str">
+      <c r="E17" s="17" t="str">
         <f t="shared" ref="E17:P17" si="6">TEXT(E18,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="F17" s="18" t="str">
+      <c r="F17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Wed</v>
       </c>
-      <c r="G17" s="18" t="str">
+      <c r="G17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Thu</v>
       </c>
-      <c r="H17" s="18" t="str">
+      <c r="H17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Fri</v>
       </c>
-      <c r="I17" s="18" t="str">
+      <c r="I17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Sat</v>
       </c>
-      <c r="J17" s="18" t="str">
+      <c r="J17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Sun</v>
       </c>
-      <c r="K17" s="18" t="str">
+      <c r="K17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Mon</v>
       </c>
-      <c r="L17" s="18" t="str">
+      <c r="L17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Tue</v>
       </c>
-      <c r="M17" s="18" t="str">
+      <c r="M17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Wed</v>
       </c>
-      <c r="N17" s="18" t="str">
+      <c r="N17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Thu</v>
       </c>
-      <c r="O17" s="18" t="str">
+      <c r="O17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Fri</v>
       </c>
-      <c r="P17" s="18" t="str">
+      <c r="P17" s="17" t="str">
         <f t="shared" si="6"/>
         <v>Sat</v>
       </c>
-      <c r="Q17" s="26" t="s">
+      <c r="Q17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="27"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="29"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -3018,19 +3357,19 @@
       <c r="P18" s="7">
         <v>45626</v>
       </c>
-      <c r="Q18" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="R18" s="16" t="s">
+      <c r="Q18" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="S18" s="16" t="s">
+      <c r="S18" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="T18" s="16" t="s">
+      <c r="T18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="U18" s="17" t="s">
+      <c r="U18" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3063,7 +3402,7 @@
       <c r="I19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="28" t="s">
+      <c r="J19" s="20" t="s">
         <v>26</v>
       </c>
       <c r="K19" s="4" t="s">
@@ -3097,11 +3436,11 @@
         <v>1</v>
       </c>
       <c r="T19" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U19" s="10">
         <f>Q19+S19+T19</f>
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3133,7 +3472,7 @@
       <c r="I20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="29"/>
+      <c r="J20" s="21"/>
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
@@ -3165,17 +3504,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" ref="T20:T25" si="10">COUNTBLANK(D20:P20)</f>
         <v>1</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" ref="U20:U25" si="11">Q20+S20+T20</f>
+        <f t="shared" ref="U20:U25" si="10">Q20+S20+T20</f>
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" ref="A21:A23" si="12">IF(B21="","",A20+1)</f>
+        <f t="shared" ref="A21:A23" si="11">IF(B21="","",A20+1)</f>
         <v>3</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -3202,7 +3540,7 @@
       <c r="I21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="29"/>
+      <c r="J21" s="21"/>
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
@@ -3234,17 +3572,16 @@
         <v>0</v>
       </c>
       <c r="T21" s="8">
+        <v>1</v>
+      </c>
+      <c r="U21" s="10">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="U21" s="10">
-        <f t="shared" si="11"/>
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -3271,7 +3608,7 @@
       <c r="I22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="29"/>
+      <c r="J22" s="21"/>
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
@@ -3303,17 +3640,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="8">
+        <v>1</v>
+      </c>
+      <c r="U22" s="10">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="U22" s="10">
-        <f t="shared" si="11"/>
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3340,7 +3676,7 @@
       <c r="I23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="29"/>
+      <c r="J23" s="21"/>
       <c r="K23" s="4" t="s">
         <v>6</v>
       </c>
@@ -3372,11 +3708,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="8">
+        <v>1</v>
+      </c>
+      <c r="U23" s="10">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="U23" s="10">
-        <f t="shared" si="11"/>
         <v>13</v>
       </c>
     </row>
@@ -3408,7 +3743,7 @@
       <c r="I24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="29"/>
+      <c r="J24" s="21"/>
       <c r="K24" s="4" t="s">
         <v>6</v>
       </c>
@@ -3440,11 +3775,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="8">
+        <v>1</v>
+      </c>
+      <c r="U24" s="10">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="U24" s="10">
-        <f t="shared" si="11"/>
         <v>13</v>
       </c>
     </row>
@@ -3476,7 +3810,7 @@
       <c r="I25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="30"/>
+      <c r="J25" s="22"/>
       <c r="K25" s="6" t="s">
         <v>6</v>
       </c>
@@ -3508,11 +3842,10 @@
         <v>0</v>
       </c>
       <c r="T25" s="9">
+        <v>1</v>
+      </c>
+      <c r="U25" s="11">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="U25" s="11">
-        <f t="shared" si="11"/>
         <v>13</v>
       </c>
     </row>
@@ -3528,64 +3861,64 @@
     <mergeCell ref="J5:J13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:I13 K5:P13 D3:P4 J5 D17:P18">
-    <cfRule type="expression" dxfId="117" priority="120">
+    <cfRule type="expression" dxfId="144" priority="120">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:I13">
-    <cfRule type="cellIs" dxfId="116" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="24" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:I25">
-    <cfRule type="expression" dxfId="114" priority="10">
+    <cfRule type="expression" dxfId="141" priority="10">
       <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="11" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="12" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5 D5:I13 K5:P13">
-    <cfRule type="cellIs" dxfId="111" priority="121" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="121" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="122" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="122" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="expression" dxfId="109" priority="4">
+    <cfRule type="expression" dxfId="136" priority="4">
       <formula>J$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="5" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="6" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:P13">
-    <cfRule type="cellIs" dxfId="106" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="13" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="14" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:P25">
-    <cfRule type="expression" dxfId="104" priority="1">
+    <cfRule type="expression" dxfId="131" priority="1">
       <formula>K$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3596,7 +3929,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D05578-9A71-4DB0-B861-FB7B360029CD}">
-  <dimension ref="A1:AM24"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -3606,193 +3939,195 @@
     <col min="5" max="32" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="3.7109375" customWidth="1"/>
     <col min="34" max="34" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="39" width="5.7109375" customWidth="1"/>
+    <col min="40" max="40" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="21" t="s">
+    <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
-      <c r="AM2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="25"/>
     </row>
-    <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:40" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="18" t="str">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="17" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="E3" s="18" t="str">
+      <c r="E3" s="17" t="str">
         <f t="shared" ref="E3:AH3" si="0">TEXT(E4,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="Q3" s="18" t="str">
+      <c r="Q3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="R3" s="18" t="str">
+      <c r="R3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="S3" s="18" t="str">
+      <c r="S3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="T3" s="18" t="str">
+      <c r="T3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="U3" s="18" t="str">
+      <c r="U3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="V3" s="18" t="str">
+      <c r="V3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="W3" s="18" t="str">
+      <c r="W3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="X3" s="18" t="str">
+      <c r="X3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="Y3" s="18" t="str">
+      <c r="Y3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="Z3" s="18" t="str">
+      <c r="Z3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AA3" s="18" t="str">
+      <c r="AA3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AB3" s="18" t="str">
+      <c r="AB3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AC3" s="18" t="str">
+      <c r="AC3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AD3" s="18" t="str">
+      <c r="AD3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AE3" s="18" t="str">
+      <c r="AE3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AF3" s="18" t="str">
+      <c r="AF3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AG3" s="18" t="str">
+      <c r="AG3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AH3" s="18" t="str">
+      <c r="AH3" s="43" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AI3" s="26" t="s">
+      <c r="AI3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="27"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="29"/>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3892,26 +4227,29 @@
       <c r="AG4" s="7">
         <v>45656</v>
       </c>
-      <c r="AH4" s="7">
+      <c r="AH4" s="44">
         <v>45657</v>
       </c>
-      <c r="AI4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ4" s="16" t="s">
+      <c r="AI4" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AK4" s="16" t="s">
+      <c r="AK4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AL4" s="16" t="s">
+      <c r="AL4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AM4" s="17" t="s">
+      <c r="AN4" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -3921,7 +4259,7 @@
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -3942,7 +4280,7 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -3963,7 +4301,7 @@
       <c r="Q5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="34" t="s">
+      <c r="R5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="S5" s="4" t="s">
@@ -3984,7 +4322,7 @@
       <c r="X5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y5" s="34" t="s">
+      <c r="Y5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="Z5" s="4" t="s">
@@ -3993,28 +4331,28 @@
       <c r="AA5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB5" s="32" t="s">
+      <c r="AB5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="AC5" s="32" t="s">
+      <c r="AC5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="AD5" s="32" t="s">
+      <c r="AD5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="AE5" s="34" t="s">
+      <c r="AE5" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="AF5" s="34" t="s">
+      <c r="AF5" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="AG5" s="34" t="s">
+      <c r="AG5" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="AH5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI5" s="4">
+      <c r="AH5" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI5" s="3">
         <f t="shared" ref="AI5:AI13" si="1">COUNTIF(D5:AH5,"P")</f>
         <v>21</v>
       </c>
@@ -4029,12 +4367,15 @@
       <c r="AL5" s="4">
         <v>5</v>
       </c>
-      <c r="AM5" s="19">
-        <f>AI5+AK5+AL5</f>
-        <v>26</v>
+      <c r="AM5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="18">
+        <f>AI5+AK5+AL5+AM5</f>
+        <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -4044,7 +4385,7 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="32"/>
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4063,7 +4404,7 @@
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="34"/>
+      <c r="K6" s="32"/>
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4082,7 +4423,7 @@
       <c r="Q6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="34"/>
+      <c r="R6" s="32"/>
       <c r="S6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4101,23 +4442,23 @@
       <c r="X6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="34"/>
+      <c r="Y6" s="32"/>
       <c r="Z6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="34"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="34"/>
-      <c r="AH6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI6" s="4">
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -4130,15 +4471,17 @@
         <v>1</v>
       </c>
       <c r="AL6" s="4">
-        <f t="shared" ref="AL6:AL13" si="4">COUNTBLANK(D6:AH6)</f>
-        <v>10</v>
-      </c>
-      <c r="AM6" s="19">
-        <f t="shared" ref="AM6:AM13" si="5">AI6+AK6+AL6</f>
+        <v>5</v>
+      </c>
+      <c r="AM6" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN6" s="18">
+        <f t="shared" ref="AN6:AN13" si="4">AI6+AK6+AL6+AM6</f>
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -4148,7 +4491,7 @@
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4167,7 +4510,7 @@
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="34"/>
+      <c r="K7" s="32"/>
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4186,7 +4529,7 @@
       <c r="Q7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R7" s="34"/>
+      <c r="R7" s="32"/>
       <c r="S7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4205,23 +4548,23 @@
       <c r="X7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y7" s="34"/>
+      <c r="Y7" s="32"/>
       <c r="Z7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI7" s="4">
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -4234,15 +4577,17 @@
         <v>0</v>
       </c>
       <c r="AL7" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM7" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN7" s="18">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM7" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -4252,7 +4597,7 @@
       <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4271,7 +4616,7 @@
       <c r="J8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="34"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4290,7 +4635,7 @@
       <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="34"/>
+      <c r="R8" s="32"/>
       <c r="S8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4309,23 +4654,23 @@
       <c r="X8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="34"/>
+      <c r="Y8" s="32"/>
       <c r="Z8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="34"/>
-      <c r="AH8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI8" s="4">
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI8" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -4338,15 +4683,17 @@
         <v>0</v>
       </c>
       <c r="AL8" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM8" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN8" s="18">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM8" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -4356,7 +4703,7 @@
       <c r="C9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4375,7 +4722,7 @@
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="34"/>
+      <c r="K9" s="32"/>
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4394,7 +4741,7 @@
       <c r="Q9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="34"/>
+      <c r="R9" s="32"/>
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4413,23 +4760,23 @@
       <c r="X9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y9" s="34"/>
+      <c r="Y9" s="32"/>
       <c r="Z9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI9" s="4">
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="32"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -4442,15 +4789,17 @@
         <v>0</v>
       </c>
       <c r="AL9" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="18">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM9" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -4460,7 +4809,7 @@
       <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4479,7 +4828,7 @@
       <c r="J10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="34"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4498,7 +4847,7 @@
       <c r="Q10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R10" s="34"/>
+      <c r="R10" s="32"/>
       <c r="S10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4517,23 +4866,23 @@
       <c r="X10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y10" s="34"/>
+      <c r="Y10" s="32"/>
       <c r="Z10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="32"/>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="34"/>
-      <c r="AH10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI10" s="4">
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="32"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI10" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -4546,15 +4895,17 @@
         <v>0</v>
       </c>
       <c r="AL10" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="18">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM10" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -4564,7 +4915,7 @@
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="32"/>
       <c r="E11" s="4" t="s">
         <v>6</v>
       </c>
@@ -4583,7 +4934,7 @@
       <c r="J11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="34"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="4" t="s">
         <v>6</v>
       </c>
@@ -4602,7 +4953,7 @@
       <c r="Q11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="R11" s="34"/>
+      <c r="R11" s="32"/>
       <c r="S11" s="4" t="s">
         <v>24</v>
       </c>
@@ -4621,23 +4972,23 @@
       <c r="X11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Y11" s="34"/>
+      <c r="Y11" s="32"/>
       <c r="Z11" s="4" t="s">
         <v>24</v>
       </c>
       <c r="AA11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="32"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="4" t="s">
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="32"/>
+      <c r="AF11" s="32"/>
+      <c r="AG11" s="32"/>
+      <c r="AH11" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="AI11" s="4">
+      <c r="AI11" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -4650,15 +5001,17 @@
         <v>0</v>
       </c>
       <c r="AL11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="4">
+        <v>2</v>
+      </c>
+      <c r="AN11" s="18">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM11" s="19">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -4668,7 +5021,7 @@
       <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4687,7 +5040,7 @@
       <c r="J12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="34"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4706,7 +5059,7 @@
       <c r="Q12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R12" s="34"/>
+      <c r="R12" s="32"/>
       <c r="S12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4725,23 +5078,23 @@
       <c r="X12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y12" s="34"/>
+      <c r="Y12" s="32"/>
       <c r="Z12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="32"/>
-      <c r="AD12" s="32"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="34"/>
-      <c r="AH12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI12" s="4">
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="32"/>
+      <c r="AF12" s="32"/>
+      <c r="AG12" s="32"/>
+      <c r="AH12" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI12" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -4754,15 +5107,17 @@
         <v>0</v>
       </c>
       <c r="AL12" s="4">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN12" s="18">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM12" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -4772,7 +5127,7 @@
       <c r="C13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="33"/>
       <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
@@ -4791,7 +5146,7 @@
       <c r="J13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="35"/>
+      <c r="K13" s="33"/>
       <c r="L13" s="6" t="s">
         <v>13</v>
       </c>
@@ -4810,7 +5165,7 @@
       <c r="Q13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="R13" s="35"/>
+      <c r="R13" s="33"/>
       <c r="S13" s="6" t="s">
         <v>13</v>
       </c>
@@ -4829,226 +5184,227 @@
       <c r="X13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Y13" s="35"/>
+      <c r="Y13" s="33"/>
       <c r="Z13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="AA13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="33"/>
-      <c r="AE13" s="35"/>
-      <c r="AF13" s="35"/>
-      <c r="AG13" s="35"/>
-      <c r="AH13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI13" s="6">
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="33"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="33"/>
+      <c r="AH13" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI13" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AJ13" s="6">
-        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="AK13" s="6">
         <v>0</v>
       </c>
-      <c r="AK13" s="6">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
       <c r="AL13" s="6">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AM13" s="20">
-        <f t="shared" si="5"/>
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN13" s="19">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="21" t="s">
+    <row r="14" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="22"/>
-      <c r="AH15" s="22"/>
-      <c r="AI15" s="22"/>
-      <c r="AJ15" s="22"/>
-      <c r="AK15" s="22"/>
-      <c r="AL15" s="22"/>
-      <c r="AM15" s="23"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
+      <c r="AH15" s="24"/>
+      <c r="AI15" s="24"/>
+      <c r="AJ15" s="24"/>
+      <c r="AK15" s="24"/>
+      <c r="AL15" s="24"/>
+      <c r="AM15" s="24"/>
+      <c r="AN15" s="25"/>
     </row>
-    <row r="16" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:40" ht="27" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="18" t="str">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="17" t="str">
         <f>TEXT(D17,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="E16" s="18" t="str">
-        <f t="shared" ref="E16:AH16" si="6">TEXT(E17,"ddd")</f>
+      <c r="E16" s="17" t="str">
+        <f t="shared" ref="E16:AH16" si="5">TEXT(E17,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="F16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="F16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="G16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="G16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="H16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="H16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="I16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="I16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="J16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="J16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="K16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="K16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="L16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="L16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="M16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="M16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="N16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="N16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="O16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="O16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="P16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="P16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="Q16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="Q16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="R16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="R16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="S16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="S16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="T16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="T16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="U16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="U16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="V16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="V16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="W16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="W16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="X16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="X16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="Y16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="Y16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="Z16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="AA16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AA16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="AB16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AB16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="AC16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AC16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="AD16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AD16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="AE16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AE16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="AF16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AF16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="AG16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AG16" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="AH16" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AH16" s="43" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="AI16" s="26" t="s">
+      <c r="AI16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="26"/>
-      <c r="AK16" s="26"/>
-      <c r="AL16" s="26"/>
-      <c r="AM16" s="27"/>
+      <c r="AJ16" s="28"/>
+      <c r="AK16" s="28"/>
+      <c r="AL16" s="28"/>
+      <c r="AM16" s="28"/>
+      <c r="AN16" s="29"/>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -5148,26 +5504,29 @@
       <c r="AG17" s="7">
         <v>45656</v>
       </c>
-      <c r="AH17" s="7">
+      <c r="AH17" s="44">
         <v>45657</v>
       </c>
-      <c r="AI17" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ17" s="16" t="s">
+      <c r="AI17" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ17" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AK17" s="16" t="s">
+      <c r="AK17" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AL17" s="16" t="s">
+      <c r="AL17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM17" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AM17" s="17" t="s">
+      <c r="AN17" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f>IF(B18="","",1)</f>
         <v>1</v>
@@ -5178,7 +5537,7 @@
       <c r="C18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="20" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -5199,7 +5558,7 @@
       <c r="J18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="20" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="4" t="s">
@@ -5220,7 +5579,7 @@
       <c r="Q18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R18" s="28" t="s">
+      <c r="R18" s="20" t="s">
         <v>26</v>
       </c>
       <c r="S18" s="4" t="s">
@@ -5241,7 +5600,7 @@
       <c r="X18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y18" s="28" t="s">
+      <c r="Y18" s="20" t="s">
         <v>26</v>
       </c>
       <c r="Z18" s="4" t="s">
@@ -5250,48 +5609,51 @@
       <c r="AA18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB18" s="36" t="s">
+      <c r="AB18" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="AC18" s="36" t="s">
+      <c r="AC18" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="AD18" s="36" t="s">
+      <c r="AD18" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="AE18" s="28" t="s">
+      <c r="AE18" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="AF18" s="28" t="s">
+      <c r="AF18" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="AG18" s="28" t="s">
+      <c r="AG18" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="AH18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI18" s="8">
-        <f t="shared" ref="AI18:AI24" si="7">COUNTIF(D18:AH18,"P")</f>
+      <c r="AH18" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI18" s="50">
+        <f t="shared" ref="AI18:AI24" si="6">COUNTIF(D18:AH18,"P")</f>
         <v>21</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" ref="AJ18:AJ24" si="8">COUNTIF(D18:AH18,"A")</f>
+        <f t="shared" ref="AJ18:AJ24" si="7">COUNTIF(D18:AH18,"A")</f>
         <v>0</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" ref="AK18:AK24" si="9">COUNTIF(D18:AH18,"L")</f>
+        <f t="shared" ref="AK18:AK24" si="8">COUNTIF(D18:AH18,"L")</f>
         <v>0</v>
       </c>
       <c r="AL18" s="8">
         <v>5</v>
       </c>
-      <c r="AM18" s="10">
-        <f>AI18+AK18+AL18</f>
-        <v>26</v>
+      <c r="AM18" s="8">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="10">
+        <f>AI18+AK18+AL18+AM18</f>
+        <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f>IF(B19="","",A18+1)</f>
         <v>2</v>
@@ -5302,7 +5664,7 @@
       <c r="C19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="29"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="4" t="s">
         <v>6</v>
       </c>
@@ -5321,7 +5683,7 @@
       <c r="J19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K19" s="29"/>
+      <c r="K19" s="21"/>
       <c r="L19" s="4" t="s">
         <v>6</v>
       </c>
@@ -5340,7 +5702,7 @@
       <c r="Q19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R19" s="29"/>
+      <c r="R19" s="21"/>
       <c r="S19" s="4" t="s">
         <v>6</v>
       </c>
@@ -5359,46 +5721,48 @@
       <c r="X19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y19" s="29"/>
+      <c r="Y19" s="21"/>
       <c r="Z19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB19" s="37"/>
-      <c r="AC19" s="37"/>
-      <c r="AD19" s="37"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI19" s="8">
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="36"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
+      <c r="AH19" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI19" s="50">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="AJ19" s="8">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="AJ19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="AL19" s="8">
-        <f t="shared" ref="AL19:AL22" si="10">COUNTBLANK(D19:AH19)</f>
-        <v>10</v>
-      </c>
-      <c r="AM19" s="10">
-        <f t="shared" ref="AM19:AM24" si="11">AI19+AK19+AL19</f>
+        <v>5</v>
+      </c>
+      <c r="AM19" s="8">
+        <v>5</v>
+      </c>
+      <c r="AN19" s="10">
+        <f t="shared" ref="AN19:AN24" si="9">AI19+AK19+AL19+AM19</f>
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" ref="A20:A22" si="12">IF(B20="","",A19+1)</f>
+        <f t="shared" ref="A20:A22" si="10">IF(B20="","",A19+1)</f>
         <v>3</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -5407,7 +5771,7 @@
       <c r="C20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="29"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="4" t="s">
         <v>6</v>
       </c>
@@ -5426,7 +5790,7 @@
       <c r="J20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="29"/>
+      <c r="K20" s="21"/>
       <c r="L20" s="4" t="s">
         <v>6</v>
       </c>
@@ -5445,7 +5809,7 @@
       <c r="Q20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R20" s="29"/>
+      <c r="R20" s="21"/>
       <c r="S20" s="4" t="s">
         <v>6</v>
       </c>
@@ -5464,46 +5828,48 @@
       <c r="X20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y20" s="29"/>
+      <c r="Y20" s="21"/>
       <c r="Z20" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="37"/>
-      <c r="AD20" s="37"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
-      <c r="AG20" s="29"/>
-      <c r="AH20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI20" s="8">
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="36"/>
+      <c r="AE20" s="21"/>
+      <c r="AF20" s="21"/>
+      <c r="AG20" s="21"/>
+      <c r="AH20" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI20" s="50">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="AJ20" s="8">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="AJ20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="8">
+      <c r="AL20" s="8">
+        <v>5</v>
+      </c>
+      <c r="AM20" s="8">
+        <v>5</v>
+      </c>
+      <c r="AN20" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL20" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="AM20" s="10">
-        <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -5512,7 +5878,7 @@
       <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="29"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="4" t="s">
         <v>6</v>
       </c>
@@ -5531,7 +5897,7 @@
       <c r="J21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="29"/>
+      <c r="K21" s="21"/>
       <c r="L21" s="4" t="s">
         <v>6</v>
       </c>
@@ -5550,7 +5916,7 @@
       <c r="Q21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R21" s="29"/>
+      <c r="R21" s="21"/>
       <c r="S21" s="4" t="s">
         <v>6</v>
       </c>
@@ -5569,46 +5935,48 @@
       <c r="X21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y21" s="29"/>
+      <c r="Y21" s="21"/>
       <c r="Z21" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="29"/>
-      <c r="AF21" s="29"/>
-      <c r="AG21" s="29"/>
-      <c r="AH21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI21" s="8">
+      <c r="AB21" s="36"/>
+      <c r="AC21" s="36"/>
+      <c r="AD21" s="36"/>
+      <c r="AE21" s="21"/>
+      <c r="AF21" s="21"/>
+      <c r="AG21" s="21"/>
+      <c r="AH21" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI21" s="50">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="AJ21" s="8">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="AJ21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="8">
+      <c r="AL21" s="8">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="8">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL21" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="AM21" s="10">
-        <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -5617,7 +5985,7 @@
       <c r="C22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="29"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="4" t="s">
         <v>6</v>
       </c>
@@ -5636,7 +6004,7 @@
       <c r="J22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K22" s="29"/>
+      <c r="K22" s="21"/>
       <c r="L22" s="4" t="s">
         <v>6</v>
       </c>
@@ -5655,7 +6023,7 @@
       <c r="Q22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R22" s="29"/>
+      <c r="R22" s="21"/>
       <c r="S22" s="4" t="s">
         <v>6</v>
       </c>
@@ -5674,44 +6042,46 @@
       <c r="X22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y22" s="29"/>
+      <c r="Y22" s="21"/>
       <c r="Z22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AA22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AB22" s="37"/>
-      <c r="AC22" s="37"/>
-      <c r="AD22" s="37"/>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="29"/>
-      <c r="AG22" s="29"/>
-      <c r="AH22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI22" s="8">
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="21"/>
+      <c r="AG22" s="21"/>
+      <c r="AH22" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI22" s="50">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="AJ22" s="8">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="AJ22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="8">
+      <c r="AL22" s="8">
+        <v>5</v>
+      </c>
+      <c r="AM22" s="8">
+        <v>5</v>
+      </c>
+      <c r="AN22" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="8">
-        <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="AM22" s="10">
-        <f t="shared" si="11"/>
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>6</v>
       </c>
@@ -5721,7 +6091,7 @@
       <c r="C23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="29"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="13" t="s">
         <v>6</v>
       </c>
@@ -5740,7 +6110,7 @@
       <c r="J23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K23" s="29"/>
+      <c r="K23" s="21"/>
       <c r="L23" s="13" t="s">
         <v>6</v>
       </c>
@@ -5759,7 +6129,7 @@
       <c r="Q23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="R23" s="29"/>
+      <c r="R23" s="21"/>
       <c r="S23" s="13" t="s">
         <v>6</v>
       </c>
@@ -5778,44 +6148,46 @@
       <c r="X23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="29"/>
+      <c r="Y23" s="21"/>
       <c r="Z23" s="13" t="s">
         <v>6</v>
       </c>
       <c r="AA23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="37"/>
-      <c r="AD23" s="37"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
-      <c r="AG23" s="29"/>
-      <c r="AH23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI23" s="14">
+      <c r="AB23" s="36"/>
+      <c r="AC23" s="36"/>
+      <c r="AD23" s="36"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="21"/>
+      <c r="AG23" s="21"/>
+      <c r="AH23" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI23" s="51">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="AJ23" s="14">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="AJ23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="8">
+      <c r="AL23" s="14">
+        <v>5</v>
+      </c>
+      <c r="AM23" s="14">
+        <v>5</v>
+      </c>
+      <c r="AN23" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="14">
-        <f>COUNTBLANK(D23:AH23)</f>
-        <v>10</v>
-      </c>
-      <c r="AM23" s="15">
-        <f t="shared" si="11"/>
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>7</v>
       </c>
@@ -5825,7 +6197,7 @@
       <c r="C24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="31"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="6" t="s">
         <v>6</v>
       </c>
@@ -5844,7 +6216,7 @@
       <c r="J24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K24" s="31"/>
+      <c r="K24" s="34"/>
       <c r="L24" s="6" t="s">
         <v>6</v>
       </c>
@@ -5863,7 +6235,7 @@
       <c r="Q24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="R24" s="31"/>
+      <c r="R24" s="34"/>
       <c r="S24" s="6" t="s">
         <v>6</v>
       </c>
@@ -5882,192 +6254,194 @@
       <c r="X24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Y24" s="31"/>
+      <c r="Y24" s="34"/>
       <c r="Z24" s="6" t="s">
         <v>6</v>
       </c>
       <c r="AA24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AB24" s="38"/>
-      <c r="AC24" s="38"/>
-      <c r="AD24" s="38"/>
-      <c r="AE24" s="31"/>
-      <c r="AF24" s="31"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI24" s="9">
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="37"/>
+      <c r="AE24" s="34"/>
+      <c r="AF24" s="34"/>
+      <c r="AG24" s="34"/>
+      <c r="AH24" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI24" s="52">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="AJ24" s="9">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="AJ24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="9">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="9">
+      <c r="AL24" s="9">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="9">
+        <v>5</v>
+      </c>
+      <c r="AN24" s="11">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="9">
-        <f>COUNTBLANK(D24:AH24)</f>
-        <v>10</v>
-      </c>
-      <c r="AM24" s="11">
-        <f t="shared" si="11"/>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A15:AN15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="AI16:AN16"/>
+    <mergeCell ref="AD18:AD24"/>
+    <mergeCell ref="D18:D24"/>
+    <mergeCell ref="AC18:AC24"/>
+    <mergeCell ref="AE18:AE24"/>
+    <mergeCell ref="AG18:AG24"/>
+    <mergeCell ref="K18:K24"/>
+    <mergeCell ref="R18:R24"/>
+    <mergeCell ref="Y18:Y24"/>
+    <mergeCell ref="AF18:AF24"/>
+    <mergeCell ref="AB18:AB24"/>
+    <mergeCell ref="A2:AN2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="AI3:AM3"/>
+    <mergeCell ref="AI3:AN3"/>
     <mergeCell ref="AD5:AD13"/>
     <mergeCell ref="D5:D13"/>
     <mergeCell ref="K5:K13"/>
     <mergeCell ref="R5:R13"/>
     <mergeCell ref="Y5:Y13"/>
     <mergeCell ref="AF5:AF13"/>
-    <mergeCell ref="K18:K24"/>
-    <mergeCell ref="R18:R24"/>
-    <mergeCell ref="Y18:Y24"/>
-    <mergeCell ref="AF18:AF24"/>
-    <mergeCell ref="AB18:AB24"/>
-    <mergeCell ref="A15:AM15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="AI16:AM16"/>
-    <mergeCell ref="AD18:AD24"/>
-    <mergeCell ref="D18:D24"/>
-    <mergeCell ref="AC18:AC24"/>
-    <mergeCell ref="AE18:AE24"/>
-    <mergeCell ref="AG18:AG24"/>
     <mergeCell ref="AB5:AB13"/>
     <mergeCell ref="AC5:AC13"/>
     <mergeCell ref="AE5:AE13"/>
     <mergeCell ref="AG5:AG13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5 K5 R5 Y5 AB5:AG5 E5:J13 L5:Q13 S5:X13 Z5:AA13 AH5:AH13">
-    <cfRule type="cellIs" dxfId="101" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="128" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="129" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="99" priority="19">
+    <cfRule type="expression" dxfId="126" priority="19">
       <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="20" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="21" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AH4 D5 K5 R5 Y5 AB5:AG5 E5:J13 L5:Q13 S5:X13 Z5:AA13 AH5:AH13 D16:AH17">
-    <cfRule type="expression" dxfId="96" priority="127">
+    <cfRule type="expression" dxfId="123" priority="127">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:J24">
-    <cfRule type="expression" dxfId="95" priority="94">
+    <cfRule type="expression" dxfId="122" priority="94">
       <formula>E$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="95" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="96" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18">
-    <cfRule type="expression" dxfId="92" priority="91">
+    <cfRule type="expression" dxfId="119" priority="91">
       <formula>K$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="92" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="93" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18:Q24">
-    <cfRule type="expression" dxfId="89" priority="64">
+    <cfRule type="expression" dxfId="116" priority="64">
       <formula>L$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="65" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="66" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="86" priority="88">
+    <cfRule type="expression" dxfId="113" priority="88">
       <formula>R$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="89" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="90" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:X24">
-    <cfRule type="expression" dxfId="83" priority="46">
+    <cfRule type="expression" dxfId="110" priority="46">
       <formula>S$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="47" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="48" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y18">
-    <cfRule type="expression" dxfId="80" priority="85">
+    <cfRule type="expression" dxfId="107" priority="85">
       <formula>Y$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="86" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="87" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z18:AA24">
-    <cfRule type="expression" dxfId="77" priority="40">
+    <cfRule type="expression" dxfId="104" priority="40">
       <formula>Z$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="41" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="42" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB18:AG18">
-    <cfRule type="expression" dxfId="74" priority="7">
+    <cfRule type="expression" dxfId="101" priority="7">
       <formula>AB$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="8" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="9" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH18:AH24">
-    <cfRule type="expression" dxfId="71" priority="22">
+    <cfRule type="expression" dxfId="98" priority="22">
       <formula>AH$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="24" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6078,7 +6452,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA2F093-D52F-43EB-89ED-905EF626F121}">
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -6088,193 +6462,195 @@
     <col min="5" max="32" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="3.7109375" customWidth="1"/>
     <col min="34" max="34" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="39" width="5.7109375" customWidth="1"/>
+    <col min="40" max="40" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="21" t="s">
+    <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
-      <c r="AM2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="25"/>
     </row>
-    <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:40" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="18" t="str">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="17" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="E3" s="18" t="str">
+      <c r="E3" s="17" t="str">
         <f t="shared" ref="E3:AH3" si="0">TEXT(E4,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="Q3" s="18" t="str">
+      <c r="Q3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="R3" s="18" t="str">
+      <c r="R3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="S3" s="18" t="str">
+      <c r="S3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="T3" s="18" t="str">
+      <c r="T3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="U3" s="18" t="str">
+      <c r="U3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="V3" s="18" t="str">
+      <c r="V3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="W3" s="18" t="str">
+      <c r="W3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="X3" s="18" t="str">
+      <c r="X3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="Y3" s="18" t="str">
+      <c r="Y3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="Z3" s="18" t="str">
+      <c r="Z3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AA3" s="18" t="str">
+      <c r="AA3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AB3" s="18" t="str">
+      <c r="AB3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AC3" s="18" t="str">
+      <c r="AC3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AD3" s="18" t="str">
+      <c r="AD3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AE3" s="18" t="str">
+      <c r="AE3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AF3" s="18" t="str">
+      <c r="AF3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AG3" s="18" t="str">
+      <c r="AG3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AH3" s="18" t="str">
+      <c r="AH3" s="43" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AI3" s="26" t="s">
+      <c r="AI3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="27"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="29"/>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -6374,26 +6750,29 @@
       <c r="AG4" s="7">
         <v>45687</v>
       </c>
-      <c r="AH4" s="7">
+      <c r="AH4" s="44">
         <v>45688</v>
       </c>
-      <c r="AI4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ4" s="16" t="s">
+      <c r="AI4" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AK4" s="16" t="s">
+      <c r="AK4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AL4" s="16" t="s">
+      <c r="AL4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AM4" s="17" t="s">
+      <c r="AN4" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -6415,7 +6794,7 @@
       <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -6436,7 +6815,7 @@
       <c r="N5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="O5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="P5" s="4" t="s">
@@ -6457,7 +6836,7 @@
       <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="34" t="s">
+      <c r="V5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="W5" s="4" t="s">
@@ -6478,13 +6857,13 @@
       <c r="AB5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC5" s="34" t="s">
+      <c r="AC5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="AD5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE5" s="42" t="s">
+      <c r="AE5" s="41" t="s">
         <v>45</v>
       </c>
       <c r="AF5" s="4" t="s">
@@ -6493,10 +6872,10 @@
       <c r="AG5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI5" s="4">
+      <c r="AH5" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI5" s="3">
         <f t="shared" ref="AI5:AI12" si="1">COUNTIF(D5:AH5,"P")</f>
         <v>26</v>
       </c>
@@ -6509,14 +6888,17 @@
         <v>0</v>
       </c>
       <c r="AL5" s="4">
-        <v>5</v>
-      </c>
-      <c r="AM5" s="19">
-        <f>AI5+AK5+AL5</f>
+        <v>1</v>
+      </c>
+      <c r="AM5" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN5" s="18">
+        <f>AI5+AK5+AL5+AM5</f>
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -6538,7 +6920,7 @@
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="32"/>
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
@@ -6557,7 +6939,7 @@
       <c r="N6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="34"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="4" t="s">
         <v>6</v>
       </c>
@@ -6576,7 +6958,7 @@
       <c r="U6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V6" s="34"/>
+      <c r="V6" s="32"/>
       <c r="W6" s="4" t="s">
         <v>6</v>
       </c>
@@ -6595,21 +6977,21 @@
       <c r="AB6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC6" s="34"/>
+      <c r="AC6" s="32"/>
       <c r="AD6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE6" s="42"/>
+      <c r="AE6" s="41"/>
       <c r="AF6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI6" s="4">
+      <c r="AH6" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -6622,15 +7004,17 @@
         <v>1</v>
       </c>
       <c r="AL6" s="4">
-        <f t="shared" ref="AL6:AL12" si="4">COUNTBLANK(D6:AH6)</f>
-        <v>5</v>
-      </c>
-      <c r="AM6" s="19">
-        <f t="shared" ref="AM6:AM12" si="5">AI6+AK6+AL6</f>
+        <v>1</v>
+      </c>
+      <c r="AM6" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="18">
+        <f t="shared" ref="AN6:AN12" si="4">AI6+AK6+AL6+AM6</f>
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -6652,7 +7036,7 @@
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="32"/>
       <c r="I7" s="4" t="s">
         <v>6</v>
       </c>
@@ -6671,7 +7055,7 @@
       <c r="N7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="34"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="4" t="s">
         <v>6</v>
       </c>
@@ -6690,7 +7074,7 @@
       <c r="U7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V7" s="34"/>
+      <c r="V7" s="32"/>
       <c r="W7" s="4" t="s">
         <v>6</v>
       </c>
@@ -6709,21 +7093,21 @@
       <c r="AB7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC7" s="34"/>
+      <c r="AC7" s="32"/>
       <c r="AD7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE7" s="42"/>
+      <c r="AE7" s="41"/>
       <c r="AF7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI7" s="4">
+      <c r="AH7" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -6736,15 +7120,17 @@
         <v>0</v>
       </c>
       <c r="AL7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="18">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AM7" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -6766,7 +7152,7 @@
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="32"/>
       <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
@@ -6785,7 +7171,7 @@
       <c r="N8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O8" s="34"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="4" t="s">
         <v>6</v>
       </c>
@@ -6804,7 +7190,7 @@
       <c r="U8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V8" s="34"/>
+      <c r="V8" s="32"/>
       <c r="W8" s="4" t="s">
         <v>6</v>
       </c>
@@ -6823,21 +7209,21 @@
       <c r="AB8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC8" s="34"/>
+      <c r="AC8" s="32"/>
       <c r="AD8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE8" s="42"/>
+      <c r="AE8" s="41"/>
       <c r="AF8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI8" s="4">
+      <c r="AH8" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI8" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -6850,15 +7236,17 @@
         <v>0</v>
       </c>
       <c r="AL8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="18">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AM8" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -6880,7 +7268,7 @@
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
@@ -6899,7 +7287,7 @@
       <c r="N9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O9" s="34"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="4" t="s">
         <v>6</v>
       </c>
@@ -6918,7 +7306,7 @@
       <c r="U9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V9" s="34"/>
+      <c r="V9" s="32"/>
       <c r="W9" s="4" t="s">
         <v>6</v>
       </c>
@@ -6937,21 +7325,21 @@
       <c r="AB9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC9" s="34"/>
+      <c r="AC9" s="32"/>
       <c r="AD9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE9" s="42"/>
+      <c r="AE9" s="41"/>
       <c r="AF9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI9" s="4">
+      <c r="AH9" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -6964,15 +7352,17 @@
         <v>0</v>
       </c>
       <c r="AL9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="18">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AM9" s="19">
-        <f t="shared" si="5"/>
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -6994,7 +7384,7 @@
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
@@ -7013,7 +7403,7 @@
       <c r="N10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O10" s="34"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="4" t="s">
         <v>6</v>
       </c>
@@ -7032,7 +7422,7 @@
       <c r="U10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V10" s="34"/>
+      <c r="V10" s="32"/>
       <c r="W10" s="4" t="s">
         <v>6</v>
       </c>
@@ -7051,21 +7441,21 @@
       <c r="AB10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC10" s="34"/>
+      <c r="AC10" s="32"/>
       <c r="AD10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE10" s="42"/>
+      <c r="AE10" s="41"/>
       <c r="AF10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI10" s="4">
+      <c r="AH10" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI10" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -7078,15 +7468,17 @@
         <v>1</v>
       </c>
       <c r="AL10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN10" s="18">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AM10" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -7108,7 +7500,7 @@
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="4" t="s">
         <v>6</v>
       </c>
@@ -7127,7 +7519,7 @@
       <c r="N11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O11" s="34"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="4" t="s">
         <v>6</v>
       </c>
@@ -7146,7 +7538,7 @@
       <c r="U11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V11" s="34"/>
+      <c r="V11" s="32"/>
       <c r="W11" s="4" t="s">
         <v>6</v>
       </c>
@@ -7165,21 +7557,21 @@
       <c r="AB11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC11" s="34"/>
+      <c r="AC11" s="32"/>
       <c r="AD11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE11" s="42"/>
+      <c r="AE11" s="41"/>
       <c r="AF11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI11" s="4">
+      <c r="AH11" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI11" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -7192,15 +7584,17 @@
         <v>1</v>
       </c>
       <c r="AL11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN11" s="18">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AM11" s="19">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -7222,7 +7616,7 @@
       <c r="G12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="33"/>
       <c r="I12" s="6" t="s">
         <v>6</v>
       </c>
@@ -7241,7 +7635,7 @@
       <c r="N12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="O12" s="35"/>
+      <c r="O12" s="33"/>
       <c r="P12" s="6" t="s">
         <v>6</v>
       </c>
@@ -7260,7 +7654,7 @@
       <c r="U12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="V12" s="35"/>
+      <c r="V12" s="33"/>
       <c r="W12" s="6" t="s">
         <v>6</v>
       </c>
@@ -7279,21 +7673,21 @@
       <c r="AB12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AC12" s="35"/>
+      <c r="AC12" s="33"/>
       <c r="AD12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE12" s="43"/>
+      <c r="AE12" s="42"/>
       <c r="AF12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="AG12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AH12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI12" s="6">
+      <c r="AH12" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI12" s="5">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -7306,197 +7700,201 @@
         <v>0</v>
       </c>
       <c r="AL12" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="19">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AM12" s="20">
-        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="21" t="s">
+    <row r="13" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
-      <c r="AH14" s="22"/>
-      <c r="AI14" s="22"/>
-      <c r="AJ14" s="22"/>
-      <c r="AK14" s="22"/>
-      <c r="AL14" s="22"/>
-      <c r="AM14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="24"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="24"/>
+      <c r="AL14" s="24"/>
+      <c r="AM14" s="24"/>
+      <c r="AN14" s="25"/>
     </row>
-    <row r="15" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:40" ht="27" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="18" t="str">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="17" t="str">
         <f>TEXT(D16,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="E15" s="18" t="str">
-        <f t="shared" ref="E15:AH15" si="6">TEXT(E16,"ddd")</f>
+      <c r="E15" s="17" t="str">
+        <f t="shared" ref="E15:AH15" si="5">TEXT(E16,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="F15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="G15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="G15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="H15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="H15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="I15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="I15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="J15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="J15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="K15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="K15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="L15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="L15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="M15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="M15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="N15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="N15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="O15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="O15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="P15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="P15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="Q15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="Q15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="R15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="R15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="S15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="S15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="T15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="T15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="U15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="U15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="V15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="V15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="W15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="W15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="X15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="X15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="Y15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="Y15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="Z15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="AA15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AA15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="AB15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AB15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sat</v>
       </c>
-      <c r="AC15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AC15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Sun</v>
       </c>
-      <c r="AD15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AD15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="AE15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AE15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Tue</v>
       </c>
-      <c r="AF15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AF15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Wed</v>
       </c>
-      <c r="AG15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AG15" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="AH15" s="18" t="str">
-        <f t="shared" si="6"/>
+      <c r="AH15" s="43" t="str">
+        <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="AI15" s="26" t="s">
+      <c r="AI15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AJ15" s="26"/>
-      <c r="AK15" s="26"/>
-      <c r="AL15" s="26"/>
-      <c r="AM15" s="27"/>
+      <c r="AJ15" s="28"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="28"/>
+      <c r="AM15" s="28"/>
+      <c r="AN15" s="29"/>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -7596,26 +7994,29 @@
       <c r="AG16" s="7">
         <v>45687</v>
       </c>
-      <c r="AH16" s="7">
+      <c r="AH16" s="44">
         <v>45688</v>
       </c>
-      <c r="AI16" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ16" s="16" t="s">
+      <c r="AI16" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AK16" s="16" t="s">
+      <c r="AK16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AL16" s="16" t="s">
+      <c r="AL16" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AM16" s="17" t="s">
+      <c r="AN16" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f>IF(B17="","",1)</f>
         <v>1</v>
@@ -7638,7 +8039,7 @@
       <c r="G17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I17" s="4" t="s">
@@ -7659,7 +8060,7 @@
       <c r="N17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O17" s="28" t="s">
+      <c r="O17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="P17" s="4" t="s">
@@ -7680,7 +8081,7 @@
       <c r="U17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V17" s="28" t="s">
+      <c r="V17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="W17" s="4" t="s">
@@ -7701,13 +8102,13 @@
       <c r="AB17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC17" s="28" t="s">
+      <c r="AC17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="AD17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE17" s="39" t="s">
+      <c r="AE17" s="38" t="s">
         <v>45</v>
       </c>
       <c r="AF17" s="4" t="s">
@@ -7716,30 +8117,33 @@
       <c r="AG17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI17" s="8">
-        <f t="shared" ref="AI17:AI23" si="7">COUNTIF(D17:AH17,"P")</f>
+      <c r="AH17" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI17" s="50">
+        <f t="shared" ref="AI17:AI23" si="6">COUNTIF(D17:AH17,"P")</f>
         <v>25</v>
       </c>
       <c r="AJ17" s="8">
-        <f t="shared" ref="AJ17:AJ23" si="8">COUNTIF(D17:AH17,"A")</f>
+        <f t="shared" ref="AJ17:AJ23" si="7">COUNTIF(D17:AH17,"A")</f>
         <v>0</v>
       </c>
       <c r="AK17" s="8">
-        <f t="shared" ref="AK17:AK23" si="9">COUNTIF(D17:AH17,"L")</f>
+        <f t="shared" ref="AK17:AK23" si="8">COUNTIF(D17:AH17,"L")</f>
         <v>1</v>
       </c>
-      <c r="AL17" s="8">
-        <v>5</v>
-      </c>
-      <c r="AM17" s="10">
-        <f>AI17+AK17+AL17</f>
+      <c r="AL17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="8">
+        <v>4</v>
+      </c>
+      <c r="AN17" s="10">
+        <f>AI17+AK17+AL17+AM17</f>
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f>IF(B18="","",A17+1)</f>
         <v>2</v>
@@ -7762,7 +8166,7 @@
       <c r="G18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H18" s="29"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="4" t="s">
         <v>6</v>
       </c>
@@ -7781,7 +8185,7 @@
       <c r="N18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O18" s="29"/>
+      <c r="O18" s="21"/>
       <c r="P18" s="4" t="s">
         <v>6</v>
       </c>
@@ -7800,7 +8204,7 @@
       <c r="U18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V18" s="29"/>
+      <c r="V18" s="21"/>
       <c r="W18" s="4" t="s">
         <v>6</v>
       </c>
@@ -7819,44 +8223,46 @@
       <c r="AB18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AC18" s="29"/>
+      <c r="AC18" s="21"/>
       <c r="AD18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE18" s="40"/>
+      <c r="AE18" s="39"/>
       <c r="AF18" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI18" s="8">
+      <c r="AH18" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI18" s="50">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="AJ18" s="8">
         <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="AJ18" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="8">
-        <f t="shared" ref="AL18:AL21" si="10">COUNTBLANK(D18:AH18)</f>
-        <v>5</v>
-      </c>
-      <c r="AM18" s="10">
-        <f t="shared" ref="AM18:AM23" si="11">AI18+AK18+AL18</f>
+      <c r="AL18" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="8">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="10">
+        <f t="shared" ref="AN18:AN23" si="9">AI18+AK18+AL18+AM18</f>
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <f t="shared" ref="A19:A21" si="12">IF(B19="","",A18+1)</f>
+        <f t="shared" ref="A19:A21" si="10">IF(B19="","",A18+1)</f>
         <v>3</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -7877,7 +8283,7 @@
       <c r="G19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="29"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="4" t="s">
         <v>6</v>
       </c>
@@ -7896,7 +8302,7 @@
       <c r="N19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O19" s="29"/>
+      <c r="O19" s="21"/>
       <c r="P19" s="4" t="s">
         <v>6</v>
       </c>
@@ -7915,7 +8321,7 @@
       <c r="U19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V19" s="29"/>
+      <c r="V19" s="21"/>
       <c r="W19" s="4" t="s">
         <v>6</v>
       </c>
@@ -7934,504 +8340,514 @@
       <c r="AB19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AC19" s="29"/>
+      <c r="AC19" s="21"/>
       <c r="AD19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE19" s="40"/>
+      <c r="AE19" s="39"/>
       <c r="AF19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI19" s="8">
+      <c r="AH19" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI19" s="50">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="AJ19" s="8">
         <f t="shared" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="AJ19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="8">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AL19" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="8">
+        <v>4</v>
+      </c>
+      <c r="AN19" s="10">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="21"/>
+      <c r="I20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O20" s="21"/>
+      <c r="P20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V20" s="21"/>
+      <c r="W20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC20" s="21"/>
+      <c r="AD20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE20" s="39"/>
+      <c r="AF20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH20" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI20" s="50">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="AJ20" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="8">
+      <c r="AL20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="8">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="10">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AL19" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="AM19" s="10">
-        <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H20" s="29"/>
-      <c r="I20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O20" s="29"/>
-      <c r="P20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V20" s="29"/>
-      <c r="W20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="X20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE20" s="40"/>
-      <c r="AF20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI20" s="8">
+      <c r="B21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" s="21"/>
+      <c r="I21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O21" s="21"/>
+      <c r="P21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V21" s="21"/>
+      <c r="W21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC21" s="21"/>
+      <c r="AD21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE21" s="39"/>
+      <c r="AF21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH21" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI21" s="50">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="AJ21" s="8">
         <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="AJ20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="8">
+      <c r="AL21" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="8">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="10">
         <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>6</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="O22" s="21"/>
+      <c r="P22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="S22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="T22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="U22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="V22" s="21"/>
+      <c r="W22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="X22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE22" s="39"/>
+      <c r="AF22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH22" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI22" s="51">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="AJ22" s="14">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="8">
-        <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="AM20" s="10">
-        <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H21" s="29"/>
-      <c r="I21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O21" s="29"/>
-      <c r="P21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="T21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V21" s="29"/>
-      <c r="W21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC21" s="29"/>
-      <c r="AD21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE21" s="40"/>
-      <c r="AF21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI21" s="8">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="AJ21" s="8">
+      <c r="AK22" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="8">
+      <c r="AL22" s="13">
+        <v>1</v>
+      </c>
+      <c r="AM22" s="14">
+        <v>4</v>
+      </c>
+      <c r="AN22" s="10">
         <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>7</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" s="22"/>
+      <c r="I23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O23" s="22"/>
+      <c r="P23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="U23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V23" s="22"/>
+      <c r="W23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE23" s="40"/>
+      <c r="AF23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH23" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI23" s="52">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="AJ23" s="9">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="8">
-        <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="AM21" s="10">
-        <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>6</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O22" s="29"/>
-      <c r="P22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="S22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="T22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="U22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="V22" s="29"/>
-      <c r="W22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="X22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE22" s="40"/>
-      <c r="AF22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI22" s="14">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="AJ22" s="14">
+      <c r="AK23" s="9">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="8">
+      <c r="AL23" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM23" s="9">
+        <v>4</v>
+      </c>
+      <c r="AN23" s="11">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="14">
-        <f>COUNTBLANK(D22:AH22)</f>
-        <v>5</v>
-      </c>
-      <c r="AM22" s="15">
-        <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
-        <v>7</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H23" s="30"/>
-      <c r="I23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="N23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O23" s="30"/>
-      <c r="P23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="R23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="S23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="T23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="U23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="V23" s="30"/>
-      <c r="W23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="X23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE23" s="41"/>
-      <c r="AF23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI23" s="9">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="AJ23" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK23" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="9">
-        <f>COUNTBLANK(D23:AH23)</f>
-        <v>5</v>
-      </c>
-      <c r="AM23" s="11">
-        <f t="shared" si="11"/>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A2:AN2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="AI3:AM3"/>
+    <mergeCell ref="AI3:AN3"/>
     <mergeCell ref="AC5:AC12"/>
     <mergeCell ref="AE17:AE23"/>
     <mergeCell ref="H5:H12"/>
@@ -8442,141 +8858,141 @@
     <mergeCell ref="V17:V23"/>
     <mergeCell ref="AC17:AC23"/>
     <mergeCell ref="AE5:AE12"/>
-    <mergeCell ref="A14:AM14"/>
+    <mergeCell ref="A14:AN14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="AI15:AM15"/>
+    <mergeCell ref="AI15:AN15"/>
   </mergeCells>
   <conditionalFormatting sqref="D17:G23">
-    <cfRule type="expression" dxfId="68" priority="40">
+    <cfRule type="expression" dxfId="95" priority="40">
       <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="41" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="42" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AH4 H5 O5 V5 AC5 AE5 D5:G12 I5:N12 P5:U12 W5:AB12 AD5:AD12 AF5:AH12 D15:AH16">
-    <cfRule type="expression" dxfId="65" priority="115">
+    <cfRule type="expression" dxfId="92" priority="115">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5 O5 V5 AC5 AE5 D5:G12 I5:N12 P5:U12 W5:AB12 AD5:AD12 AF5:AH12">
-    <cfRule type="cellIs" dxfId="64" priority="116" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="116" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="117" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="117" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="62" priority="37">
+    <cfRule type="expression" dxfId="89" priority="37">
       <formula>H$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="38" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="39" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17:N23">
-    <cfRule type="expression" dxfId="59" priority="25">
+    <cfRule type="expression" dxfId="86" priority="25">
       <formula>I$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="26" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O17">
-    <cfRule type="expression" dxfId="56" priority="34">
+    <cfRule type="expression" dxfId="83" priority="34">
       <formula>O$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="35" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="36" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P17:U23">
-    <cfRule type="expression" dxfId="53" priority="22">
+    <cfRule type="expression" dxfId="80" priority="22">
       <formula>P$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="24" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17">
-    <cfRule type="expression" dxfId="50" priority="31">
+    <cfRule type="expression" dxfId="77" priority="31">
       <formula>V$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="32" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="33" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W17:AB23">
-    <cfRule type="expression" dxfId="47" priority="16">
+    <cfRule type="expression" dxfId="74" priority="16">
       <formula>W$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="17" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="18" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC17">
-    <cfRule type="expression" dxfId="44" priority="28">
+    <cfRule type="expression" dxfId="71" priority="28">
       <formula>AC$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="29" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="30" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD17:AD23">
-    <cfRule type="expression" dxfId="41" priority="13">
+    <cfRule type="expression" dxfId="68" priority="13">
       <formula>AD$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="14" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="15" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE17">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>AE$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF17:AH23">
-    <cfRule type="expression" dxfId="35" priority="4">
+    <cfRule type="expression" dxfId="62" priority="4">
       <formula>AF$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="5" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="6" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8587,131 +9003,190 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD7C6B6-F721-45FE-A56A-F79E8ECB6487}">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="20" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="5.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="20" width="3.7109375" customWidth="1"/>
+    <col min="21" max="31" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="36" width="5.7109375" customWidth="1"/>
+    <col min="37" max="37" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="21" t="s">
+    <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:37" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="25"/>
     </row>
-    <row r="3" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:37" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="18" t="str">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="17" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="E3" s="18" t="str">
-        <f t="shared" ref="E3:T3" si="0">TEXT(E4,"ddd")</f>
+      <c r="E3" s="17" t="str">
+        <f t="shared" ref="E3:AE3" si="0">TEXT(E4,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="Q3" s="18" t="str">
+      <c r="Q3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="R3" s="18" t="str">
+      <c r="R3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="S3" s="18" t="str">
+      <c r="S3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="T3" s="18" t="str">
+      <c r="T3" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="U3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="V3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="W3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="X3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="Y3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="Z3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="AA3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="AB3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="AC3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="AD3" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="AE3" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="AF3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="27"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="29"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -8772,23 +9247,59 @@
       <c r="T4" s="7">
         <v>45705</v>
       </c>
-      <c r="U4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="V4" s="16" t="s">
+      <c r="U4" s="7">
+        <v>45706</v>
+      </c>
+      <c r="V4" s="7">
+        <v>45707</v>
+      </c>
+      <c r="W4" s="7">
+        <v>45708</v>
+      </c>
+      <c r="X4" s="7">
+        <v>45709</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>45710</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>45711</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>45712</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>45713</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>45714</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>45715</v>
+      </c>
+      <c r="AE4" s="44">
+        <v>45716</v>
+      </c>
+      <c r="AF4" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="W4" s="16" t="s">
+      <c r="AH4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="X4" s="16" t="s">
+      <c r="AI4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="AK4" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -8801,7 +9312,7 @@
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -8810,8 +9321,8 @@
       <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>6</v>
+      <c r="H5" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>6</v>
@@ -8822,7 +9333,7 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
@@ -8837,39 +9348,75 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="42" t="s">
+      <c r="Q5" s="41" t="s">
         <v>47</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="34" t="s">
+      <c r="S5" s="32" t="s">
         <v>26</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U5" s="4">
-        <f t="shared" ref="U5:U12" si="1">COUNTIF(D5:T5,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V5" s="4">
-        <f t="shared" ref="V5:V12" si="2">COUNTIF(D5:T5,"A")</f>
+      <c r="U5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="3">
+        <f>COUNTIF(D5:AE5,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG5" s="4">
+        <f>COUNTIF(D5:AE5,"A")</f>
         <v>0</v>
       </c>
-      <c r="W5" s="4">
-        <f t="shared" ref="W5:W12" si="3">COUNTIF(D5:T5,"L")</f>
+      <c r="AH5" s="4">
+        <f>COUNTIF(D5:AE5,"L")</f>
         <v>0</v>
       </c>
-      <c r="X5" s="4">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="19">
-        <f>U5+W5+X5</f>
-        <v>18</v>
+      <c r="AI5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK5" s="18">
+        <f>AF5+AH5+AI5+AJ5</f>
+        <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -8882,16 +9429,14 @@
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="34"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H6" s="41"/>
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
@@ -8901,7 +9446,7 @@
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="4" t="s">
         <v>6</v>
       </c>
@@ -8914,36 +9459,67 @@
       <c r="P6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="42"/>
+      <c r="Q6" s="41"/>
       <c r="R6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S6" s="34"/>
+      <c r="S6" s="32"/>
       <c r="T6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U6" s="4">
-        <f t="shared" si="1"/>
+      <c r="U6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="41"/>
+      <c r="W6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="4">
-        <f t="shared" si="2"/>
+      <c r="Y6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="3">
+        <f>COUNTIF(D6:AE6,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AG6" s="4">
+        <f>COUNTIF(D6:AE6,"A")</f>
         <v>0</v>
       </c>
-      <c r="W6" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="4">
-        <f t="shared" ref="X6:X12" si="4">COUNTBLANK(D6:T6)</f>
+      <c r="AH6" s="4">
+        <f>COUNTIF(D6:AE6,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AI6" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ6" s="4">
         <v>4</v>
       </c>
-      <c r="Y6" s="19">
-        <f t="shared" ref="Y6:Y12" si="5">U6+W6+X6</f>
-        <v>17</v>
+      <c r="AK6" s="18">
+        <f t="shared" ref="AK6:AK12" si="1">AF6+AH6+AI6+AJ6</f>
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -8956,16 +9532,14 @@
       <c r="D7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="34"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H7" s="41"/>
       <c r="I7" s="4" t="s">
         <v>6</v>
       </c>
@@ -8975,7 +9549,7 @@
       <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="32"/>
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
@@ -8988,36 +9562,67 @@
       <c r="P7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q7" s="42"/>
+      <c r="Q7" s="41"/>
       <c r="R7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="34"/>
+      <c r="S7" s="32"/>
       <c r="T7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="41"/>
+      <c r="W7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="3">
+        <f>COUNTIF(D7:AE7,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AG7" s="4">
+        <f>COUNTIF(D7:AE7,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f>COUNTIF(D7:AE7,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="18">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="V7" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W7" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="X7" s="4">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="Y7" s="19">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -9030,16 +9635,14 @@
       <c r="D8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="34"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H8" s="41"/>
       <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
@@ -9049,7 +9652,7 @@
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="4" t="s">
         <v>6</v>
       </c>
@@ -9062,36 +9665,67 @@
       <c r="P8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q8" s="42"/>
+      <c r="Q8" s="41"/>
       <c r="R8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S8" s="34"/>
+      <c r="S8" s="32"/>
       <c r="T8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V8" s="41"/>
+      <c r="W8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE8" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="3">
+        <f>COUNTIF(D8:AE8,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="AG8" s="4">
+        <f>COUNTIF(D8:AE8,"A")</f>
+        <v>2</v>
+      </c>
+      <c r="AH8" s="4">
+        <f>COUNTIF(D8:AE8,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="18">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="V8" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="W8" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="X8" s="4">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="Y8" s="19">
-        <f t="shared" si="5"/>
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -9104,16 +9738,14 @@
       <c r="D9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="34"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H9" s="41"/>
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
@@ -9123,7 +9755,7 @@
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="32"/>
       <c r="M9" s="4" t="s">
         <v>6</v>
       </c>
@@ -9136,36 +9768,67 @@
       <c r="P9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q9" s="42"/>
+      <c r="Q9" s="41"/>
       <c r="R9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="34"/>
+      <c r="S9" s="32"/>
       <c r="T9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="41"/>
+      <c r="W9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF9" s="3">
+        <f>COUNTIF(D9:AE9,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG9" s="4">
+        <f>COUNTIF(D9:AE9,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="4">
+        <f>COUNTIF(D9:AE9,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="18">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V9" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="4">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="Y9" s="19">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -9178,16 +9841,14 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="34"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H10" s="41"/>
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
@@ -9197,7 +9858,7 @@
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="4" t="s">
         <v>6</v>
       </c>
@@ -9210,36 +9871,67 @@
       <c r="P10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q10" s="42"/>
+      <c r="Q10" s="41"/>
       <c r="R10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="34"/>
+      <c r="S10" s="32"/>
       <c r="T10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V10" s="41"/>
+      <c r="W10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE10" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF10" s="3">
+        <f>COUNTIF(D10:AE10,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG10" s="4">
+        <f>COUNTIF(D10:AE10,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="4">
+        <f>COUNTIF(D10:AE10,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="18">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V10" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="4">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="Y10" s="19">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -9252,16 +9944,14 @@
       <c r="D11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="34"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H11" s="41"/>
       <c r="I11" s="4" t="s">
         <v>6</v>
       </c>
@@ -9271,7 +9961,7 @@
       <c r="K11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="32"/>
       <c r="M11" s="4" t="s">
         <v>6</v>
       </c>
@@ -9284,36 +9974,67 @@
       <c r="P11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q11" s="42"/>
+      <c r="Q11" s="41"/>
       <c r="R11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="34"/>
+      <c r="S11" s="32"/>
       <c r="T11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U11" s="4">
+      <c r="U11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V11" s="41"/>
+      <c r="W11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="32"/>
+      <c r="AA11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE11" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF11" s="3">
+        <f>COUNTIF(D11:AE11,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG11" s="4">
+        <f>COUNTIF(D11:AE11,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="4">
+        <f>COUNTIF(D11:AE11,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK11" s="18">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V11" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="4">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="Y11" s="19">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -9326,16 +10047,14 @@
       <c r="D12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="33"/>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="H12" s="42"/>
       <c r="I12" s="6" t="s">
         <v>6</v>
       </c>
@@ -9345,161 +10064,249 @@
       <c r="K12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L12" s="35"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="43"/>
+      <c r="Q12" s="42"/>
       <c r="R12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S12" s="35"/>
+      <c r="S12" s="33"/>
       <c r="T12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V12" s="42"/>
+      <c r="W12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE12" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF12" s="5">
+        <f>COUNTIF(D12:AE12,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AG12" s="6">
+        <f>COUNTIF(D12:AE12,"A")</f>
+        <v>2</v>
+      </c>
+      <c r="AH12" s="6">
+        <f>COUNTIF(D12:AE12,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AK12" s="19">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V12" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:37" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="24"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="25"/>
+    </row>
+    <row r="15" spans="1:37" ht="27" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="17" t="str">
+        <f>TEXT(D16,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="E15" s="17" t="str">
+        <f t="shared" ref="E15:AE15" si="2">TEXT(E16,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="F15" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="6">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="Y12" s="20">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
+        <v>Mon</v>
+      </c>
+      <c r="G15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="H15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="I15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="J15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="K15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="L15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sun</v>
+      </c>
+      <c r="M15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="N15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="O15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="P15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="R15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="S15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sun</v>
+      </c>
+      <c r="T15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="U15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="V15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="W15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="X15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="Y15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="Z15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Sun</v>
+      </c>
+      <c r="AA15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="AB15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="AC15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="AD15" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="AE15" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="AF15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="28"/>
+      <c r="AK15" s="29"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="23"/>
-    </row>
-    <row r="15" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="18" t="str">
-        <f>TEXT(D16,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="E15" s="18" t="str">
-        <f t="shared" ref="E15:T15" si="6">TEXT(E16,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Fri</v>
-      </c>
-      <c r="G15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Sat</v>
-      </c>
-      <c r="H15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Sun</v>
-      </c>
-      <c r="I15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Mon</v>
-      </c>
-      <c r="J15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Tue</v>
-      </c>
-      <c r="K15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Wed</v>
-      </c>
-      <c r="L15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Thu</v>
-      </c>
-      <c r="M15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Fri</v>
-      </c>
-      <c r="N15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Sat</v>
-      </c>
-      <c r="O15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Sun</v>
-      </c>
-      <c r="P15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Mon</v>
-      </c>
-      <c r="Q15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Tue</v>
-      </c>
-      <c r="R15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Wed</v>
-      </c>
-      <c r="S15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Thu</v>
-      </c>
-      <c r="T15" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v>Fri</v>
-      </c>
-      <c r="U15" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="V15" s="26"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="26"/>
-      <c r="Y15" s="27"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -9510,73 +10317,109 @@
         <v>4</v>
       </c>
       <c r="D16" s="7">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="E16" s="7">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="F16" s="7">
-        <v>45660</v>
+        <v>45691</v>
       </c>
       <c r="G16" s="7">
-        <v>45661</v>
+        <v>45692</v>
       </c>
       <c r="H16" s="7">
-        <v>45662</v>
+        <v>45693</v>
       </c>
       <c r="I16" s="7">
-        <v>45663</v>
+        <v>45694</v>
       </c>
       <c r="J16" s="7">
-        <v>45664</v>
+        <v>45695</v>
       </c>
       <c r="K16" s="7">
-        <v>45665</v>
+        <v>45696</v>
       </c>
       <c r="L16" s="7">
-        <v>45666</v>
+        <v>45697</v>
       </c>
       <c r="M16" s="7">
-        <v>45667</v>
+        <v>45698</v>
       </c>
       <c r="N16" s="7">
-        <v>45668</v>
+        <v>45699</v>
       </c>
       <c r="O16" s="7">
-        <v>45669</v>
+        <v>45700</v>
       </c>
       <c r="P16" s="7">
-        <v>45670</v>
+        <v>45701</v>
       </c>
       <c r="Q16" s="7">
-        <v>45671</v>
+        <v>45702</v>
       </c>
       <c r="R16" s="7">
-        <v>45672</v>
+        <v>45703</v>
       </c>
       <c r="S16" s="7">
-        <v>45673</v>
+        <v>45704</v>
       </c>
       <c r="T16" s="7">
-        <v>45674</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="V16" s="16" t="s">
+        <v>45705</v>
+      </c>
+      <c r="U16" s="7">
+        <v>45706</v>
+      </c>
+      <c r="V16" s="7">
+        <v>45707</v>
+      </c>
+      <c r="W16" s="7">
+        <v>45708</v>
+      </c>
+      <c r="X16" s="7">
+        <v>45709</v>
+      </c>
+      <c r="Y16" s="7">
+        <v>45710</v>
+      </c>
+      <c r="Z16" s="7">
+        <v>45711</v>
+      </c>
+      <c r="AA16" s="7">
+        <v>45712</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>45713</v>
+      </c>
+      <c r="AC16" s="7">
+        <v>45714</v>
+      </c>
+      <c r="AD16" s="7">
+        <v>45715</v>
+      </c>
+      <c r="AE16" s="44">
+        <v>45716</v>
+      </c>
+      <c r="AF16" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="W16" s="16" t="s">
+      <c r="AH16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="X16" s="16" t="s">
+      <c r="AI16" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="Y16" s="17" t="s">
+      <c r="AK16" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f>IF(B17="","",1)</f>
         <v>1</v>
@@ -9590,7 +10433,7 @@
       <c r="D17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -9599,8 +10442,8 @@
       <c r="G17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>6</v>
+      <c r="H17" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
@@ -9611,7 +10454,7 @@
       <c r="K17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L17" s="28" t="s">
+      <c r="L17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="M17" s="4" t="s">
@@ -9626,38 +10469,75 @@
       <c r="P17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q17" s="42" t="s">
+      <c r="Q17" s="41" t="s">
         <v>47</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S17" s="28" t="s">
+      <c r="S17" s="20" t="s">
         <v>26</v>
       </c>
       <c r="T17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U17" s="8">
-        <f>COUNTIF(D17:T17,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V17" s="8">
-        <f>COUNTIF(D17:T17,"A")</f>
+      <c r="U17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V17" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE17" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF17" s="50">
+        <f>COUNTIF(D17:AE17,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG17" s="8">
+        <f>COUNTIF(D17:AE17,"A")</f>
         <v>0</v>
       </c>
-      <c r="W17" s="8">
-        <f>COUNTIF(D17:T17,"L")</f>
+      <c r="AH17" s="8">
+        <f>COUNTIF(D17:AE17,"L")</f>
         <v>0</v>
       </c>
-      <c r="X17" s="8">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="4" t="s">
-        <v>6</v>
+      <c r="AI17" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="8">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="18">
+        <f>AF17+AH17+AI17+AJ17</f>
+        <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f>IF(B18="","",A17+1)</f>
         <v>2</v>
@@ -9671,16 +10551,14 @@
       <c r="D18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="29"/>
+      <c r="E18" s="21"/>
       <c r="F18" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H18" s="41"/>
       <c r="I18" s="4" t="s">
         <v>6</v>
       </c>
@@ -9690,7 +10568,7 @@
       <c r="K18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L18" s="29"/>
+      <c r="L18" s="21"/>
       <c r="M18" s="4" t="s">
         <v>6</v>
       </c>
@@ -9703,37 +10581,69 @@
       <c r="P18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q18" s="42"/>
+      <c r="Q18" s="41"/>
       <c r="R18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S18" s="29"/>
+      <c r="S18" s="21"/>
       <c r="T18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U18" s="8">
-        <f>COUNTIF(D18:T18,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V18" s="8">
-        <f>COUNTIF(D18:T18,"A")</f>
+      <c r="U18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V18" s="41"/>
+      <c r="W18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE18" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF18" s="50">
+        <f>COUNTIF(D18:AE18,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG18" s="8">
+        <f>COUNTIF(D18:AE18,"A")</f>
         <v>0</v>
       </c>
-      <c r="W18" s="8">
-        <f>COUNTIF(D18:T18,"L")</f>
+      <c r="AH18" s="8">
+        <f>COUNTIF(D18:AE18,"L")</f>
         <v>0</v>
       </c>
-      <c r="X18" s="8">
-        <f>COUNTBLANK(D18:T18)</f>
+      <c r="AI18" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="8">
         <v>4</v>
       </c>
-      <c r="Y18" s="4" t="s">
-        <v>6</v>
+      <c r="AK18" s="18">
+        <f t="shared" ref="AK18:AK24" si="3">AF18+AH18+AI18+AJ18</f>
+        <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <f t="shared" ref="A19:A24" si="7">IF(B19="","",A18+1)</f>
+        <f t="shared" ref="A19:A24" si="4">IF(B19="","",A18+1)</f>
         <v>3</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -9745,16 +10655,14 @@
       <c r="D19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="29"/>
+      <c r="E19" s="21"/>
       <c r="F19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H19" s="41"/>
       <c r="I19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9764,7 +10672,7 @@
       <c r="K19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L19" s="29"/>
+      <c r="L19" s="21"/>
       <c r="M19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9777,37 +10685,69 @@
       <c r="P19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q19" s="42"/>
+      <c r="Q19" s="41"/>
       <c r="R19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="29"/>
+      <c r="S19" s="21"/>
       <c r="T19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U19" s="8">
-        <f>COUNTIF(D19:T19,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V19" s="8">
-        <f>COUNTIF(D19:T19,"A")</f>
+      <c r="U19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V19" s="41"/>
+      <c r="W19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE19" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF19" s="50">
+        <f>COUNTIF(D19:AE19,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG19" s="8">
+        <f>COUNTIF(D19:AE19,"A")</f>
         <v>0</v>
       </c>
-      <c r="W19" s="8">
-        <f>COUNTIF(D19:T19,"L")</f>
+      <c r="AH19" s="8">
+        <f>COUNTIF(D19:AE19,"L")</f>
         <v>0</v>
       </c>
-      <c r="X19" s="8">
-        <f>COUNTBLANK(D19:T19)</f>
+      <c r="AI19" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ19" s="8">
         <v>4</v>
       </c>
-      <c r="Y19" s="4" t="s">
-        <v>6</v>
+      <c r="AK19" s="18">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -9819,16 +10759,14 @@
       <c r="D20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="29"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H20" s="41"/>
       <c r="I20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9838,7 +10776,7 @@
       <c r="K20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="29"/>
+      <c r="L20" s="21"/>
       <c r="M20" s="4" t="s">
         <v>6</v>
       </c>
@@ -9851,37 +10789,69 @@
       <c r="P20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q20" s="42"/>
+      <c r="Q20" s="41"/>
       <c r="R20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S20" s="29"/>
+      <c r="S20" s="21"/>
       <c r="T20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U20" s="8">
-        <f>COUNTIF(D20:T20,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V20" s="8">
-        <f>COUNTIF(D20:T20,"A")</f>
+      <c r="U20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V20" s="41"/>
+      <c r="W20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE20" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF20" s="50">
+        <f>COUNTIF(D20:AE20,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG20" s="8">
+        <f>COUNTIF(D20:AE20,"A")</f>
         <v>0</v>
       </c>
-      <c r="W20" s="8">
-        <f>COUNTIF(D20:T20,"L")</f>
+      <c r="AH20" s="8">
+        <f>COUNTIF(D20:AE20,"L")</f>
         <v>0</v>
       </c>
-      <c r="X20" s="8">
-        <f>COUNTBLANK(D20:T20)</f>
+      <c r="AI20" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ20" s="8">
         <v>4</v>
       </c>
-      <c r="Y20" s="4" t="s">
-        <v>6</v>
+      <c r="AK20" s="18">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -9893,16 +10863,14 @@
       <c r="D21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="29"/>
+      <c r="E21" s="21"/>
       <c r="F21" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H21" s="41"/>
       <c r="I21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9912,7 +10880,7 @@
       <c r="K21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="29"/>
+      <c r="L21" s="21"/>
       <c r="M21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9925,37 +10893,69 @@
       <c r="P21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q21" s="42"/>
+      <c r="Q21" s="41"/>
       <c r="R21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S21" s="29"/>
+      <c r="S21" s="21"/>
       <c r="T21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U21" s="8">
-        <f>COUNTIF(D21:T21,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V21" s="8">
-        <f>COUNTIF(D21:T21,"A")</f>
+      <c r="U21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V21" s="41"/>
+      <c r="W21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE21" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF21" s="50">
+        <f>COUNTIF(D21:AE21,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG21" s="8">
+        <f>COUNTIF(D21:AE21,"A")</f>
         <v>0</v>
       </c>
-      <c r="W21" s="8">
-        <f>COUNTIF(D21:T21,"L")</f>
+      <c r="AH21" s="8">
+        <f>COUNTIF(D21:AE21,"L")</f>
         <v>0</v>
       </c>
-      <c r="X21" s="8">
-        <f>COUNTBLANK(D21:T21)</f>
+      <c r="AI21" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="8">
         <v>4</v>
       </c>
-      <c r="Y21" s="4" t="s">
-        <v>6</v>
+      <c r="AK21" s="18">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -9967,16 +10967,14 @@
       <c r="D22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="29"/>
+      <c r="E22" s="21"/>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="H22" s="41"/>
       <c r="I22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9986,7 +10984,7 @@
       <c r="K22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="29"/>
+      <c r="L22" s="21"/>
       <c r="M22" s="4" t="s">
         <v>6</v>
       </c>
@@ -9999,25 +10997,69 @@
       <c r="P22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q22" s="42"/>
+      <c r="Q22" s="41"/>
       <c r="R22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="29"/>
+      <c r="S22" s="21"/>
       <c r="T22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="14"/>
+      <c r="U22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="41"/>
+      <c r="W22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="Y22" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE22" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF22" s="50">
+        <f>COUNTIF(D22:AE22,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AG22" s="8">
+        <f>COUNTIF(D22:AE22,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="8">
+        <f>COUNTIF(D22:AE22,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AI22" s="4">
+        <v>3</v>
+      </c>
+      <c r="AJ22" s="8">
+        <v>4</v>
+      </c>
+      <c r="AK22" s="18">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -10029,16 +11071,14 @@
       <c r="D23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="29"/>
+      <c r="E23" s="21"/>
       <c r="F23" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>6</v>
-      </c>
+      <c r="H23" s="41"/>
       <c r="I23" s="13" t="s">
         <v>6</v>
       </c>
@@ -10048,7 +11088,7 @@
       <c r="K23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="29"/>
+      <c r="L23" s="21"/>
       <c r="M23" s="13" t="s">
         <v>6</v>
       </c>
@@ -10061,37 +11101,69 @@
       <c r="P23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="Q23" s="42"/>
+      <c r="Q23" s="41"/>
       <c r="R23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="S23" s="29"/>
+      <c r="S23" s="21"/>
       <c r="T23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="U23" s="14">
-        <f>COUNTIF(D23:T23,"P")</f>
+      <c r="U23" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="V23" s="14">
-        <f>COUNTIF(D23:T23,"A")</f>
+      <c r="V23" s="41"/>
+      <c r="W23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="X23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE23" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF23" s="51">
+        <f>COUNTIF(D23:AE23,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AG23" s="14">
+        <f>COUNTIF(D23:AE23,"A")</f>
         <v>0</v>
       </c>
-      <c r="W23" s="8">
-        <f>COUNTIF(D23:T23,"L")</f>
-        <v>0</v>
-      </c>
-      <c r="X23" s="14">
-        <f>COUNTBLANK(D23:T23)</f>
+      <c r="AH23" s="8">
+        <f>COUNTIF(D23:AE23,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="AI23" s="13">
+        <v>3</v>
+      </c>
+      <c r="AJ23" s="14">
         <v>4</v>
       </c>
-      <c r="Y23" s="13" t="s">
-        <v>6</v>
+      <c r="AK23" s="18">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -10103,16 +11175,14 @@
       <c r="D24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="30"/>
+      <c r="E24" s="22"/>
       <c r="F24" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="H24" s="42"/>
       <c r="I24" s="6" t="s">
         <v>6</v>
       </c>
@@ -10122,7 +11192,7 @@
       <c r="K24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L24" s="30"/>
+      <c r="L24" s="22"/>
       <c r="M24" s="6" t="s">
         <v>6</v>
       </c>
@@ -10135,171 +11205,312 @@
       <c r="P24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q24" s="43"/>
+      <c r="Q24" s="42"/>
       <c r="R24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S24" s="30"/>
+      <c r="S24" s="22"/>
       <c r="T24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="U24" s="9">
-        <f>COUNTIF(D24:T24,"P")</f>
-        <v>13</v>
-      </c>
-      <c r="V24" s="9">
-        <f>COUNTIF(D24:T24,"A")</f>
+      <c r="U24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V24" s="42"/>
+      <c r="W24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE24" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF24" s="52">
+        <f>COUNTIF(D24:AE24,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AG24" s="9">
+        <f>COUNTIF(D24:AE24,"A")</f>
         <v>0</v>
       </c>
-      <c r="W24" s="9">
-        <f>COUNTIF(D24:T24,"L")</f>
+      <c r="AH24" s="9">
+        <f>COUNTIF(D24:AE24,"L")</f>
         <v>0</v>
       </c>
-      <c r="X24" s="9">
-        <f>COUNTBLANK(D24:T24)</f>
+      <c r="AI24" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ24" s="9">
         <v>4</v>
       </c>
-      <c r="Y24" s="6" t="s">
-        <v>6</v>
+      <c r="AK24" s="19">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A2:Y2"/>
+  <mergeCells count="20">
+    <mergeCell ref="H17:H24"/>
+    <mergeCell ref="Q17:Q24"/>
+    <mergeCell ref="S17:S24"/>
+    <mergeCell ref="Z17:Z24"/>
+    <mergeCell ref="V5:V12"/>
+    <mergeCell ref="V17:V24"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="A14:AK14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="AF15:AK15"/>
+    <mergeCell ref="L5:L12"/>
+    <mergeCell ref="Q5:Q12"/>
+    <mergeCell ref="S5:S12"/>
+    <mergeCell ref="Z5:Z12"/>
+    <mergeCell ref="L17:L24"/>
+    <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="AF3:AK3"/>
     <mergeCell ref="E5:E12"/>
-    <mergeCell ref="L5:L12"/>
-    <mergeCell ref="S5:S12"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="L17:L24"/>
-    <mergeCell ref="S17:S24"/>
-    <mergeCell ref="Q5:Q12"/>
-    <mergeCell ref="Q17:Q24"/>
-    <mergeCell ref="A14:Y14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="U15:Y15"/>
+    <mergeCell ref="H5:H12"/>
   </mergeCells>
   <conditionalFormatting sqref="D17:D24">
-    <cfRule type="expression" dxfId="32" priority="124">
+    <cfRule type="expression" dxfId="59" priority="166">
       <formula>D$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="167" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="168" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:T4 E5 L5 Q5 S5 D5:D12 F5:K12 M5:P12 R5:R12 T5:T12 D15:T16">
-    <cfRule type="expression" dxfId="29" priority="175">
+  <conditionalFormatting sqref="E5 D5:D12 L5 Q5 S5 F5:G12 M5:P12 R5:R12 D3:AE4 Z5 T5:U12 AA5:AE12 D15:AE16 W5:Y12 V5 I5:K12 H5">
+    <cfRule type="expression" dxfId="56" priority="217">
       <formula>D$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 L5 Q5 S5 D5:D12 F5:K12 M5:P12 R5:R12 T5:T12">
-    <cfRule type="cellIs" dxfId="28" priority="176" operator="equal">
+  <conditionalFormatting sqref="E5 D5:D12 L5 Q5 S5 F5:G12 M5:P12 R5:R12 Z5 T5:U12 AA5:AE12 W5:Y12 V5 I5:K12 H5">
+    <cfRule type="cellIs" dxfId="55" priority="218" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="177" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="219" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" dxfId="26" priority="85">
+    <cfRule type="expression" dxfId="53" priority="127">
       <formula>E$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="128" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="129" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:K24">
-    <cfRule type="expression" dxfId="23" priority="55">
+  <conditionalFormatting sqref="U17:U24 F17:G24 I17:K24">
+    <cfRule type="expression" dxfId="50" priority="97">
       <formula>F$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="98" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="99" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X17:Y24">
+    <cfRule type="expression" dxfId="47" priority="85">
+      <formula>X$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="86" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="87" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE17:AE24">
+    <cfRule type="expression" dxfId="44" priority="76">
+      <formula>AE$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="77" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="78" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="expression" dxfId="20" priority="82">
+    <cfRule type="expression" dxfId="41" priority="40">
       <formula>L$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="42" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17:P24">
-    <cfRule type="expression" dxfId="17" priority="43">
+    <cfRule type="expression" dxfId="38" priority="34">
       <formula>M$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="35" priority="25">
       <formula>Q$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="26" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="27" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17:R24">
-    <cfRule type="expression" dxfId="11" priority="37">
+    <cfRule type="expression" dxfId="32" priority="31">
       <formula>R$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="33" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S17">
-    <cfRule type="expression" dxfId="8" priority="79">
+    <cfRule type="expression" dxfId="29" priority="37">
       <formula>S$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="38" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="39" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T17:T24">
-    <cfRule type="expression" dxfId="5" priority="34">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>T$3="SUN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="29" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y17:Y24">
-    <cfRule type="expression" dxfId="2" priority="61">
-      <formula>Y$3="SUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="62" operator="equal">
+  <conditionalFormatting sqref="W17:W24">
+    <cfRule type="expression" dxfId="23" priority="22">
+      <formula>W$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="24" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA17:AA24">
+    <cfRule type="expression" dxfId="20" priority="19">
+      <formula>AA$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB17:AB24">
+    <cfRule type="expression" dxfId="17" priority="16">
+      <formula>AB$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC17:AC24">
+    <cfRule type="expression" dxfId="14" priority="13">
+      <formula>AC$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD17:AD24">
+    <cfRule type="expression" dxfId="11" priority="10">
+      <formula>AD$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z17">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>Z$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V17">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>V$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V17">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>H$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
